--- a/Assessment Questions/AIE/ADS-114/Gen AI and Agentic AI Essentials/Orchestration Frameworks/Orchestration Frameworks.xlsx
+++ b/Assessment Questions/AIE/ADS-114/Gen AI and Agentic AI Essentials/Orchestration Frameworks/Orchestration Frameworks.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orchestration_Frameworks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,11 @@
           <t>Type</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -447,6 +452,11 @@
           <t>Theory</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -462,6 +472,11 @@
           <t>Theory</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -477,6 +492,11 @@
           <t>Theory</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -492,6 +512,11 @@
           <t>Theory</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -522,6 +547,11 @@
           <t>Theory</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -552,6 +582,11 @@
           <t>Theory</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -567,6 +602,11 @@
           <t>Theory</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -612,6 +652,11 @@
           <t>Practical</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -627,6 +672,11 @@
           <t>Practical</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -657,6 +707,11 @@
           <t>Practical</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -672,6 +727,11 @@
           <t>Practical</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -687,6 +747,11 @@
           <t>Practical</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -702,6 +767,11 @@
           <t>Practical</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -713,6 +783,11 @@
         </is>
       </c>
       <c r="C20" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Practical</t>
         </is>
